--- a/server/DS_Mentor_email.xlsx
+++ b/server/DS_Mentor_email.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\project\exe\jumpln-app-backend-java-spring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\project\exe\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68183BD5-AECA-4B1D-8E80-3A83093C8D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D895E99F-7A0D-4B77-B334-4922F5907D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXE101" sheetId="3" state="hidden" r:id="rId1"/>
@@ -7057,10 +7057,10 @@
     <t>CS190452</t>
   </si>
   <si>
-    <t>djnd</t>
-  </si>
-  <si>
-    <t>voanhbendjnd@gmail.com</t>
+    <t>voanhben111@gmail.com</t>
+  </si>
+  <si>
+    <t>trang</t>
   </si>
 </sst>
 </file>
@@ -7545,26 +7545,26 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:N572"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.7109375" style="3"/>
+    <col min="15" max="16384" width="10.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>537</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>72</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>108</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>73</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>74</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>143</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>144</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>109</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>3</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>145</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>75</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>146</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>110</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>111</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>147</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>76</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>77</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>5</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>148</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>6</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>112</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>78</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>7</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>538</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>79</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>113</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>149</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>150</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>80</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>114</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>8</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>539</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>151</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>81</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>540</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>115</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>116</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>152</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>9</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>10</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>153</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>541</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>11</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>154</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>117</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>155</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>542</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>12</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>118</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>156</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>13</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>157</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>543</v>
       </c>
@@ -10520,7 +10520,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>544</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>82</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>119</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>83</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>158</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>84</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>85</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>120</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>14</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>86</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>545</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>546</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>121</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>547</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>122</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>159</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>548</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>160</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>161</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>549</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>15</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>16</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>123</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>550</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>17</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>162</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>163</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>87</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>88</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>18</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>89</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>19</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>90</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>20</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>91</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>164</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>21</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>22</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>551</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>552</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>92</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>23</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>93</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>553</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>94</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>165</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>125</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>166</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>95</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>96</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>554</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>126</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>167</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>168</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>97</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>555</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>556</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>127</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>24</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>557</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>128</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>98</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>558</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>25</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>559</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>99</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>560</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>561</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>26</v>
       </c>
@@ -12760,7 +12760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>129</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>562</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>130</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>563</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>100</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>564</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>131</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>27</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>132</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>133</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>565</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>566</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>169</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>170</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>101</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>171</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -13368,7 +13368,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -13720,7 +13720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -14008,7 +14008,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -14136,7 +14136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -14264,7 +14264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -14360,7 +14360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -14488,7 +14488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -14776,7 +14776,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -14936,7 +14936,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -15032,7 +15032,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -15224,7 +15224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -15448,7 +15448,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -15480,7 +15480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>247</v>
       </c>
@@ -15512,7 +15512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>248</v>
       </c>
@@ -15544,7 +15544,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>249</v>
       </c>
@@ -15576,7 +15576,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>250</v>
       </c>
@@ -15608,7 +15608,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>251</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>252</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>253</v>
       </c>
@@ -15704,7 +15704,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>254</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>255</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>256</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>257</v>
       </c>
@@ -15832,7 +15832,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>258</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>259</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>260</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>261</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>262</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>263</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>264</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>265</v>
       </c>
@@ -16088,7 +16088,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>266</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>267</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>268</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>269</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>270</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>271</v>
       </c>
@@ -16280,7 +16280,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>272</v>
       </c>
@@ -16312,7 +16312,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>273</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>274</v>
       </c>
@@ -16376,7 +16376,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>275</v>
       </c>
@@ -16408,7 +16408,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>276</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>277</v>
       </c>
@@ -16472,7 +16472,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>278</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>280</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>281</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>282</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>283</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>284</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>285</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>286</v>
       </c>
@@ -16760,7 +16760,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>287</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>288</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>289</v>
       </c>
@@ -16856,7 +16856,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>290</v>
       </c>
@@ -16888,7 +16888,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>291</v>
       </c>
@@ -16920,7 +16920,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>292</v>
       </c>
@@ -16952,7 +16952,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>293</v>
       </c>
@@ -16984,7 +16984,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>294</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -17048,7 +17048,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>296</v>
       </c>
@@ -17080,7 +17080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>298</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -17176,7 +17176,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>300</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>302</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>304</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>306</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>307</v>
       </c>
@@ -17432,7 +17432,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>308</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>309</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>310</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>311</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>312</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>313</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>314</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>315</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>316</v>
       </c>
@@ -17720,7 +17720,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>317</v>
       </c>
@@ -17752,7 +17752,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>318</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>319</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>320</v>
       </c>
@@ -17848,7 +17848,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>322</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -17944,7 +17944,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>324</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>326</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>327</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>328</v>
       </c>
@@ -18104,7 +18104,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>329</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>330</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>331</v>
       </c>
@@ -18200,7 +18200,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>332</v>
       </c>
@@ -18232,7 +18232,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>333</v>
       </c>
@@ -18264,7 +18264,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>334</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>335</v>
       </c>
@@ -18328,7 +18328,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>336</v>
       </c>
@@ -18360,7 +18360,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>337</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>338</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>339</v>
       </c>
@@ -18456,7 +18456,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>340</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>341</v>
       </c>
@@ -18520,7 +18520,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>342</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -18584,7 +18584,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>344</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>346</v>
       </c>
@@ -18680,7 +18680,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>347</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>348</v>
       </c>
@@ -18744,7 +18744,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -18776,7 +18776,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>350</v>
       </c>
@@ -18808,7 +18808,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>351</v>
       </c>
@@ -18840,7 +18840,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>352</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>353</v>
       </c>
@@ -18904,7 +18904,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>354</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>355</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>356</v>
       </c>
@@ -19000,7 +19000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>357</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>358</v>
       </c>
@@ -19064,7 +19064,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>359</v>
       </c>
@@ -19096,7 +19096,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>360</v>
       </c>
@@ -19128,7 +19128,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>361</v>
       </c>
@@ -19160,7 +19160,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>362</v>
       </c>
@@ -19192,7 +19192,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>363</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -19256,7 +19256,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>366</v>
       </c>
@@ -19320,7 +19320,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>368</v>
       </c>
@@ -19384,7 +19384,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -19416,7 +19416,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>370</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -19480,7 +19480,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>372</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>374</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>376</v>
       </c>
@@ -19640,7 +19640,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -19672,7 +19672,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>378</v>
       </c>
@@ -19704,7 +19704,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>379</v>
       </c>
@@ -19736,7 +19736,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>380</v>
       </c>
@@ -19768,7 +19768,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>381</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>382</v>
       </c>
@@ -19832,7 +19832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>383</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>384</v>
       </c>
@@ -19896,7 +19896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>385</v>
       </c>
@@ -19928,7 +19928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>386</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>388</v>
       </c>
@@ -20024,7 +20024,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>390</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -20120,7 +20120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>392</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>394</v>
       </c>
@@ -20216,7 +20216,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>396</v>
       </c>
@@ -20280,7 +20280,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>397</v>
       </c>
@@ -20312,7 +20312,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>398</v>
       </c>
@@ -20344,7 +20344,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>399</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>400</v>
       </c>
@@ -20408,7 +20408,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>401</v>
       </c>
@@ -20440,7 +20440,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>402</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>403</v>
       </c>
@@ -20504,7 +20504,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>404</v>
       </c>
@@ -20536,7 +20536,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>406</v>
       </c>
@@ -20600,7 +20600,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>408</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -20696,7 +20696,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>410</v>
       </c>
@@ -20728,7 +20728,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -20760,7 +20760,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>412</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>414</v>
       </c>
@@ -20856,7 +20856,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>416</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>417</v>
       </c>
@@ -20952,7 +20952,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>418</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -21016,7 +21016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>420</v>
       </c>
@@ -21048,7 +21048,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>422</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>424</v>
       </c>
@@ -21176,7 +21176,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>426</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -21272,7 +21272,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>428</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>429</v>
       </c>
@@ -21336,7 +21336,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>430</v>
       </c>
@@ -21368,7 +21368,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>432</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>433</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>434</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>436</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="438" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -21592,7 +21592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>438</v>
       </c>
@@ -21624,7 +21624,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -21656,7 +21656,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>440</v>
       </c>
@@ -21688,7 +21688,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>442</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="444" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>444</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -21848,7 +21848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>446</v>
       </c>
@@ -21880,7 +21880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="448" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>447</v>
       </c>
@@ -21912,7 +21912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>448</v>
       </c>
@@ -21944,7 +21944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>449</v>
       </c>
@@ -21976,7 +21976,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>450</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>451</v>
       </c>
@@ -22040,7 +22040,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>452</v>
       </c>
@@ -22072,7 +22072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>453</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>454</v>
       </c>
@@ -22136,7 +22136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>455</v>
       </c>
@@ -22168,7 +22168,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>456</v>
       </c>
@@ -22200,7 +22200,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>457</v>
       </c>
@@ -22232,7 +22232,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>458</v>
       </c>
@@ -22264,7 +22264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>459</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>460</v>
       </c>
@@ -22328,7 +22328,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>461</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>462</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>463</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>464</v>
       </c>
@@ -22456,7 +22456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>465</v>
       </c>
@@ -22488,7 +22488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="467" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>466</v>
       </c>
@@ -22520,7 +22520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>467</v>
       </c>
@@ -22552,7 +22552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>468</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>469</v>
       </c>
@@ -22616,7 +22616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>470</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="472" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>471</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>472</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>473</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>474</v>
       </c>
@@ -22776,7 +22776,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>475</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="477" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>476</v>
       </c>
@@ -22840,7 +22840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>477</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>478</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>479</v>
       </c>
@@ -22936,7 +22936,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>480</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>481</v>
       </c>
@@ -23000,7 +23000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>482</v>
       </c>
@@ -23032,7 +23032,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>483</v>
       </c>
@@ -23064,7 +23064,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>484</v>
       </c>
@@ -23096,7 +23096,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>485</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>486</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="488" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>487</v>
       </c>
@@ -23192,7 +23192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="489" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>488</v>
       </c>
@@ -23224,7 +23224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="490" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>489</v>
       </c>
@@ -23256,7 +23256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3">
         <v>490</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="492" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>491</v>
       </c>
@@ -23320,7 +23320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3">
         <v>492</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>493</v>
       </c>
@@ -23384,7 +23384,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3">
         <v>494</v>
       </c>
@@ -23416,7 +23416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>495</v>
       </c>
@@ -23448,7 +23448,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="497" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3">
         <v>496</v>
       </c>
@@ -23480,7 +23480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="498" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>497</v>
       </c>
@@ -23512,7 +23512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="499" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3">
         <v>498</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="500" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>499</v>
       </c>
@@ -23576,7 +23576,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="501" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3">
         <v>500</v>
       </c>
@@ -23608,7 +23608,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="502" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>501</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="503" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3">
         <v>502</v>
       </c>
@@ -23672,7 +23672,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="504" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>503</v>
       </c>
@@ -23704,7 +23704,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="505" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3">
         <v>504</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="506" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>505</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="507" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3">
         <v>506</v>
       </c>
@@ -23800,7 +23800,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="508" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>507</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3">
         <v>508</v>
       </c>
@@ -23864,7 +23864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="510" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3">
         <v>509</v>
       </c>
@@ -23896,7 +23896,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="511" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3">
         <v>510</v>
       </c>
@@ -23928,7 +23928,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="512" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3">
         <v>511</v>
       </c>
@@ -23960,7 +23960,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="513" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3">
         <v>512</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="514" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3">
         <v>513</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="515" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3">
         <v>514</v>
       </c>
@@ -24056,7 +24056,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="516" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3">
         <v>515</v>
       </c>
@@ -24088,7 +24088,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="517" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3">
         <v>516</v>
       </c>
@@ -24120,7 +24120,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="518" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3">
         <v>517</v>
       </c>
@@ -24152,7 +24152,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="519" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3">
         <v>518</v>
       </c>
@@ -24184,7 +24184,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3">
         <v>519</v>
       </c>
@@ -24216,7 +24216,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3">
         <v>520</v>
       </c>
@@ -24248,7 +24248,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="522" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3">
         <v>521</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3">
         <v>522</v>
       </c>
@@ -24312,7 +24312,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3">
         <v>523</v>
       </c>
@@ -24344,7 +24344,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="525" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3">
         <v>524</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="526" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3">
         <v>525</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="527" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3">
         <v>526</v>
       </c>
@@ -24440,7 +24440,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="528" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3">
         <v>527</v>
       </c>
@@ -24472,7 +24472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="529" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="3">
         <v>528</v>
       </c>
@@ -24504,7 +24504,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="530" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="3">
         <v>529</v>
       </c>
@@ -24536,7 +24536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="531" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="3">
         <v>530</v>
       </c>
@@ -24568,7 +24568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="532" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3">
         <v>531</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="533" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3">
         <v>532</v>
       </c>
@@ -24632,7 +24632,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="534" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3">
         <v>533</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="535" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3">
         <v>534</v>
       </c>
@@ -24696,7 +24696,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="536" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="3">
         <v>535</v>
       </c>
@@ -24728,7 +24728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="537" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3">
         <v>536</v>
       </c>
@@ -24760,7 +24760,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" s="3">
         <v>172</v>
       </c>
@@ -24792,7 +24792,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A539" s="3">
         <v>567</v>
       </c>
@@ -24824,7 +24824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A540" s="3">
         <v>134</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A541" s="3">
         <v>173</v>
       </c>
@@ -24888,7 +24888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A542" s="3">
         <v>28</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A543" s="3">
         <v>29</v>
       </c>
@@ -24952,7 +24952,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" s="3">
         <v>30</v>
       </c>
@@ -24984,7 +24984,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" s="3">
         <v>31</v>
       </c>
@@ -25016,7 +25016,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" s="3">
         <v>568</v>
       </c>
@@ -25048,7 +25048,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" s="3">
         <v>102</v>
       </c>
@@ -25080,7 +25080,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="3">
         <v>103</v>
       </c>
@@ -25112,7 +25112,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="3">
         <v>104</v>
       </c>
@@ -25144,7 +25144,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="3">
         <v>174</v>
       </c>
@@ -25176,7 +25176,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" s="3">
         <v>175</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" s="3">
         <v>569</v>
       </c>
@@ -25240,7 +25240,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" s="3">
         <v>32</v>
       </c>
@@ -25272,7 +25272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A554" s="3">
         <v>176</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A555" s="3">
         <v>105</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A556" s="3">
         <v>135</v>
       </c>
@@ -25368,7 +25368,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A557" s="3">
         <v>33</v>
       </c>
@@ -25400,7 +25400,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A558" s="3">
         <v>136</v>
       </c>
@@ -25432,7 +25432,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A559" s="3">
         <v>177</v>
       </c>
@@ -25464,7 +25464,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A560" s="3">
         <v>570</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A561" s="3">
         <v>137</v>
       </c>
@@ -25528,7 +25528,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A562" s="3">
         <v>106</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A563" s="3">
         <v>34</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A564" s="3">
         <v>571</v>
       </c>
@@ -25624,7 +25624,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A565" s="3">
         <v>107</v>
       </c>
@@ -25656,7 +25656,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A566" s="3">
         <v>35</v>
       </c>
@@ -25688,7 +25688,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A567" s="3">
         <v>138</v>
       </c>
@@ -25720,7 +25720,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A568" s="3">
         <v>36</v>
       </c>
@@ -25752,7 +25752,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A569" s="3">
         <v>139</v>
       </c>
@@ -25784,7 +25784,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A570" s="3">
         <v>140</v>
       </c>
@@ -25816,7 +25816,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A571" s="3">
         <v>141</v>
       </c>
@@ -25848,7 +25848,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A572" s="3">
         <v>142</v>
       </c>
@@ -25903,15 +25903,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8403D725-964A-41D0-8E58-9A354E36CA30}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="19.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="19.85546875" style="5"/>
+    <col min="1" max="1" width="7.109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="19.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="6" t="s">
         <v>52</v>
@@ -25920,15 +25920,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2340</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>2341</v>
       </c>
     </row>
   </sheetData>

--- a/server/DS_Mentor_email.xlsx
+++ b/server/DS_Mentor_email.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\project\exe\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D895E99F-7A0D-4B77-B334-4922F5907D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1B173B-4F0B-483B-B84B-BBE60E215458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5157" uniqueCount="2342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5159" uniqueCount="2344">
   <si>
     <t>GroupName</t>
   </si>
@@ -7057,10 +7057,16 @@
     <t>CS190452</t>
   </si>
   <si>
+    <t>djnd</t>
+  </si>
+  <si>
+    <t>voanhbendjndnd@gmail.com</t>
+  </si>
+  <si>
+    <t>misaka</t>
+  </si>
+  <si>
     <t>voanhben111@gmail.com</t>
-  </si>
-  <si>
-    <t>trang</t>
   </si>
 </sst>
 </file>
@@ -7080,7 +7086,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
     </font>
@@ -7093,15 +7107,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
     </font>
@@ -7127,13 +7133,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
+        <fgColor rgb="FFCAEDFB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAEDFB"/>
+        <fgColor rgb="FFC0E6F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7170,7 +7176,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
@@ -7184,23 +7190,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -25902,38 +25908,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8403D725-964A-41D0-8E58-9A354E36CA30}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="19.88671875" style="5"/>
+    <col min="1" max="1" width="7.109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="19.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="9"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2341</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>2340</v>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>2343</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{AE987024-25C6-48D1-A252-A73471C60A6E}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{14E9D22C-F6B5-4BD9-9D70-9AEEDC41C0C1}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{FDC32AE0-5942-4745-8EF1-07AEA6AB4DE1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/server/DS_Mentor_email.xlsx
+++ b/server/DS_Mentor_email.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\project\exe\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1B173B-4F0B-483B-B84B-BBE60E215458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D895E99F-7A0D-4B77-B334-4922F5907D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5159" uniqueCount="2344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5157" uniqueCount="2342">
   <si>
     <t>GroupName</t>
   </si>
@@ -7057,16 +7057,10 @@
     <t>CS190452</t>
   </si>
   <si>
-    <t>djnd</t>
-  </si>
-  <si>
-    <t>voanhbendjndnd@gmail.com</t>
-  </si>
-  <si>
-    <t>misaka</t>
-  </si>
-  <si>
     <t>voanhben111@gmail.com</t>
+  </si>
+  <si>
+    <t>trang</t>
   </si>
 </sst>
 </file>
@@ -7086,15 +7080,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
     </font>
@@ -7107,7 +7093,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
     </font>
@@ -7133,13 +7127,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAEDFB"/>
+        <fgColor rgb="FFC0E6F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
+        <fgColor rgb="FFCAEDFB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7176,7 +7170,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
@@ -7190,23 +7184,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -25908,50 +25902,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8403D725-964A-41D0-8E58-9A354E36CA30}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="19.88671875" style="7"/>
+    <col min="1" max="1" width="7.109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="19.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2340</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>2341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>2342</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>2343</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{14E9D22C-F6B5-4BD9-9D70-9AEEDC41C0C1}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{FDC32AE0-5942-4745-8EF1-07AEA6AB4DE1}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{AE987024-25C6-48D1-A252-A73471C60A6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
